--- a/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Downtown_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/FingerLakes Farms/FingerLakes Farms_Downtown_20260515.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -571,13 +571,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>23.75</v>
       </c>
       <c r="E10" t="n">
-        <v>47.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
